--- a/data/trans_orig/P1002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38086</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>49060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77516</t>
+          <t>79264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655926</t>
+          <t>656353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>676136</t>
+          <t>676083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641556</t>
+          <t>639291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>662788</t>
+          <t>662902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1304847</t>
+          <t>1303099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1332795</t>
+          <t>1334077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36517</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>70377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54466</t>
+          <t>54687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88200</t>
+          <t>87542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101520</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>145428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>895839</t>
+          <t>891423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>925283</t>
+          <t>923040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>880193</t>
+          <t>880851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913927</t>
+          <t>913706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1786216</t>
+          <t>1784765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1828673</t>
+          <t>1829268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102278</t>
+          <t>101554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107150</t>
+          <t>106390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>149547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619368</t>
+          <t>620302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647369</t>
+          <t>646515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>581563</t>
+          <t>582287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615852</t>
+          <t>616470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1212745</t>
+          <t>1212803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255200</t>
+          <t>1255960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66538</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76846</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115211</t>
+          <t>117032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123941</t>
+          <t>127124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170968</t>
+          <t>176632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>875684</t>
+          <t>878943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>904123</t>
+          <t>905157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>923401</t>
+          <t>921580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961766</t>
+          <t>959212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1809866</t>
+          <t>1804202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856893</t>
+          <t>1853710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146413</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197135</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253234</t>
+          <t>254321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>321680</t>
+          <t>320284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416591</t>
+          <t>416760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501248</t>
+          <t>498152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3079408</t>
+          <t>3077746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3130130</t>
+          <t>3129787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3057517</t>
+          <t>3058913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3125963</t>
+          <t>3124876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6154493</t>
+          <t>6157589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6239150</t>
+          <t>6238981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85731</t>
+          <t>86187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124592</t>
+          <t>125205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126906</t>
+          <t>128245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175547</t>
+          <t>177468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643758</t>
+          <t>642143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670740</t>
+          <t>669807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>572458</t>
+          <t>571845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>611319</t>
+          <t>610863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1224972</t>
+          <t>1223051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1273613</t>
+          <t>1272274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94437</t>
+          <t>92445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126718</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172464</t>
+          <t>174676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196397</t>
+          <t>194894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>253460</t>
+          <t>255791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922456</t>
+          <t>924448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>957211</t>
+          <t>959583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>859720</t>
+          <t>857508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>905466</t>
+          <t>903387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1795617</t>
+          <t>1793286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1852680</t>
+          <t>1854183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83359</t>
+          <t>81524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122349</t>
+          <t>123207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121265</t>
+          <t>121629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168659</t>
+          <t>169538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>697472</t>
+          <t>696918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>727305</t>
+          <t>727237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653770</t>
+          <t>652912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>692760</t>
+          <t>694595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365083</t>
+          <t>1364204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1412477</t>
+          <t>1412113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85482</t>
+          <t>84327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119683</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165108</t>
+          <t>167083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178012</t>
+          <t>181705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235393</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861320</t>
+          <t>862475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896166</t>
+          <t>895522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885848</t>
+          <t>883873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>931273</t>
+          <t>929863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1762365</t>
+          <t>1760487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1819746</t>
+          <t>1816053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202429</t>
+          <t>200223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265576</t>
+          <t>262762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>458056</t>
+          <t>458486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>540116</t>
+          <t>543955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674567</t>
+          <t>676277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>780114</t>
+          <t>777108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3159212</t>
+          <t>3162026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3222359</t>
+          <t>3224565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3016193</t>
+          <t>3012354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3098253</t>
+          <t>3097823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6200983</t>
+          <t>6203989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6306530</t>
+          <t>6304820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54576</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93575</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97366</t>
+          <t>97478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138725</t>
+          <t>139215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620224</t>
+          <t>620212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>645623</t>
+          <t>645682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>579264</t>
+          <t>578070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>613482</t>
+          <t>611257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1208914</t>
+          <t>1208424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250273</t>
+          <t>1250161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53414</t>
+          <t>55173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91884</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131972</t>
+          <t>133817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127623</t>
+          <t>129749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178472</t>
+          <t>180732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>969017</t>
+          <t>967258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993126</t>
+          <t>992654</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>910941</t>
+          <t>909096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>951029</t>
+          <t>952014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1886872</t>
+          <t>1884612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1937721</t>
+          <t>1935595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72641</t>
+          <t>71828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109159</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103983</t>
+          <t>104989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>149839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>706457</t>
+          <t>707606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>733490</t>
+          <t>732868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>675852</t>
+          <t>677374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>712370</t>
+          <t>713183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1395272</t>
+          <t>1394724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1440580</t>
+          <t>1439574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47997</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79279</t>
+          <t>82778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83289</t>
+          <t>84321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>125707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139989</t>
+          <t>142173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192220</t>
+          <t>191106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>858288</t>
+          <t>854789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>889570</t>
+          <t>887657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>919029</t>
+          <t>918072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960490</t>
+          <t>959458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1789126</t>
+          <t>1790240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1841357</t>
+          <t>1839173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157335</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209501</t>
+          <t>210026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>341007</t>
+          <t>342362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>415129</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>512014</t>
+          <t>512495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>603749</t>
+          <t>607279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3184849</t>
+          <t>3184324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3237015</t>
+          <t>3239314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3129413</t>
+          <t>3124234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3203535</t>
+          <t>3202180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6335143</t>
+          <t>6331613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6426878</t>
+          <t>6426397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46051</t>
+          <t>46332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76277</t>
+          <t>76514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82861</t>
+          <t>83467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115381</t>
+          <t>114349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>589390</t>
+          <t>589109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>611026</t>
+          <t>611457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598852</t>
+          <t>598615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620939</t>
+          <t>621202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1195190</t>
+          <t>1196222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1227710</t>
+          <t>1227104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26616</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72103</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84043</t>
+          <t>83635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114358</t>
+          <t>116730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100731</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177459</t>
+          <t>181706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1120761</t>
+          <t>1119750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166248</t>
+          <t>1167669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>843102</t>
+          <t>840730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>873417</t>
+          <t>873825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1972865</t>
+          <t>1968618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049593</t>
+          <t>2044505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>40627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71172</t>
+          <t>72139</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107936</t>
+          <t>108119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90511</t>
+          <t>87957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164613</t>
+          <t>162801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633508</t>
+          <t>632541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664667</t>
+          <t>664053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>825430</t>
+          <t>825247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>892382</t>
+          <t>898845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1473433</t>
+          <t>1475245</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1547535</t>
+          <t>1550089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100824</t>
+          <t>99191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145848</t>
+          <t>147566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145633</t>
+          <t>147385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199568</t>
+          <t>199820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862846</t>
+          <t>862277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>889038</t>
+          <t>888135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948524</t>
+          <t>946806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>993548</t>
+          <t>995181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820429</t>
+          <t>1820177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1874364</t>
+          <t>1872612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>144095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218652</t>
+          <t>218060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>297598</t>
+          <t>293952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>405500</t>
+          <t>409591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>477718</t>
+          <t>480796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>608844</t>
+          <t>614848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3239959</t>
+          <t>3240551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3314628</t>
+          <t>3314516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3254827</t>
+          <t>3250736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3362729</t>
+          <t>3366375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6510094</t>
+          <t>6504090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6641220</t>
+          <t>6638142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49060</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>49295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79264</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656353</t>
+          <t>656104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>676083</t>
+          <t>675233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639291</t>
+          <t>639687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>662902</t>
+          <t>662889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1303099</t>
+          <t>1303252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334077</t>
+          <t>1333068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38760</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>66145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87542</t>
+          <t>88434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100925</t>
+          <t>99954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145428</t>
+          <t>142858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891423</t>
+          <t>895655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>923040</t>
+          <t>923569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>880851</t>
+          <t>879959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913706</t>
+          <t>913604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1784765</t>
+          <t>1787335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1829268</t>
+          <t>1830239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58207</t>
+          <t>57750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67371</t>
+          <t>68030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101554</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149547</t>
+          <t>149106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620302</t>
+          <t>620759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646515</t>
+          <t>647388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>582287</t>
+          <t>582648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616470</t>
+          <t>615811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1212803</t>
+          <t>1213244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255960</t>
+          <t>1255314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37065</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63279</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>79470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117032</t>
+          <t>116484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127124</t>
+          <t>125205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176632</t>
+          <t>172590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878943</t>
+          <t>876221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>905157</t>
+          <t>904577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>921580</t>
+          <t>922128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959212</t>
+          <t>959142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1804202</t>
+          <t>1808244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1853710</t>
+          <t>1855629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146756</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>198912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254321</t>
+          <t>256407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>320052</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416760</t>
+          <t>417963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>498152</t>
+          <t>503940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3077746</t>
+          <t>3077631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3129787</t>
+          <t>3128079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3058913</t>
+          <t>3059145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3124876</t>
+          <t>3122790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6157589</t>
+          <t>6151801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6238981</t>
+          <t>6237778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61326</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86187</t>
+          <t>83357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125205</t>
+          <t>121814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128245</t>
+          <t>128274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177468</t>
+          <t>174323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>642143</t>
+          <t>641859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669807</t>
+          <t>671382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>571845</t>
+          <t>575236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>610863</t>
+          <t>613693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1223051</t>
+          <t>1226196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1272274</t>
+          <t>1272245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57310</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92445</t>
+          <t>93053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128797</t>
+          <t>128448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174676</t>
+          <t>174874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194894</t>
+          <t>195451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>255791</t>
+          <t>252676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924448</t>
+          <t>923840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>959583</t>
+          <t>957816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>857508</t>
+          <t>857310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>903387</t>
+          <t>903736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1793286</t>
+          <t>1796401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1854183</t>
+          <t>1853626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>31818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81524</t>
+          <t>83369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123207</t>
+          <t>121346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121629</t>
+          <t>123041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169538</t>
+          <t>169654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696918</t>
+          <t>697347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>727237</t>
+          <t>725805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652912</t>
+          <t>654773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>694595</t>
+          <t>692750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364204</t>
+          <t>1364088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1412113</t>
+          <t>1410701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>50709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84327</t>
+          <t>84450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121093</t>
+          <t>121206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167083</t>
+          <t>166821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181705</t>
+          <t>179190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237271</t>
+          <t>237212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862475</t>
+          <t>862352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895522</t>
+          <t>896093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>883873</t>
+          <t>884135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>929863</t>
+          <t>929750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1760487</t>
+          <t>1760546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1816053</t>
+          <t>1818568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>200223</t>
+          <t>203429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>262762</t>
+          <t>264601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>458486</t>
+          <t>458375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>543955</t>
+          <t>538013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676277</t>
+          <t>677517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>777108</t>
+          <t>780673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3162026</t>
+          <t>3160187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3224565</t>
+          <t>3221359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3012354</t>
+          <t>3018296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3097823</t>
+          <t>3097934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6203989</t>
+          <t>6200424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6304820</t>
+          <t>6303580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61582</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>94499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>97547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139215</t>
+          <t>139991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620212</t>
+          <t>621130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>645682</t>
+          <t>645280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>578070</t>
+          <t>578340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>611257</t>
+          <t>612026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1208424</t>
+          <t>1207648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1250161</t>
+          <t>1250092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>28523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55173</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90899</t>
+          <t>89882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133817</t>
+          <t>131496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129749</t>
+          <t>127571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180732</t>
+          <t>177980</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>967258</t>
+          <t>969313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992654</t>
+          <t>993908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909096</t>
+          <t>911417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>952014</t>
+          <t>953031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1884612</t>
+          <t>1887364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1935595</t>
+          <t>1937773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107637</t>
+          <t>109301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149839</t>
+          <t>148362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>707606</t>
+          <t>707172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>732868</t>
+          <t>734154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677374</t>
+          <t>675710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>713183</t>
+          <t>712871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1394724</t>
+          <t>1396201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1439574</t>
+          <t>1440551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>48697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82778</t>
+          <t>82404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84321</t>
+          <t>84454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125707</t>
+          <t>125048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142173</t>
+          <t>142016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191106</t>
+          <t>192467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854789</t>
+          <t>855163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887657</t>
+          <t>888870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918072</t>
+          <t>918731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959458</t>
+          <t>959325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1790240</t>
+          <t>1788879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1839173</t>
+          <t>1839330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>155036</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210026</t>
+          <t>210644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>342362</t>
+          <t>337941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>420308</t>
+          <t>419802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>512495</t>
+          <t>514784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>607279</t>
+          <t>607076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3184324</t>
+          <t>3183706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3239314</t>
+          <t>3236173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3124234</t>
+          <t>3124740</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3202180</t>
+          <t>3206601</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6331613</t>
+          <t>6331816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6426397</t>
+          <t>6424108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46332</t>
+          <t>51118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64137</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76514</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97653</t>
+          <t>107043</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83467</t>
+          <t>92156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114349</t>
+          <t>124726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>601925</t>
+          <t>653972</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>589109</t>
+          <t>639592</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>611457</t>
+          <t>664780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>610992</t>
+          <t>662207</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>598615</t>
+          <t>648330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>621202</t>
+          <t>675248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1212918</t>
+          <t>1316179</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1196222</t>
+          <t>1298496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1227104</t>
+          <t>1331066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675129</t>
+          <t>732512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310571</t>
+          <t>1423222</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>57303</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73114</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98373</t>
+          <t>109062</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83635</t>
+          <t>91022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116730</t>
+          <t>126897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>149514</t>
+          <t>166365</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105819</t>
+          <t>141938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181706</t>
+          <t>190347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1141723</t>
+          <t>991614</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1119750</t>
+          <t>976134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1167669</t>
+          <t>1004599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>859087</t>
+          <t>961036</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840730</t>
+          <t>943201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>873825</t>
+          <t>979076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2000810</t>
+          <t>1952650</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1968618</t>
+          <t>1928668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2044505</t>
+          <t>1977077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150324</t>
+          <t>2119015</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150324</t>
+          <t>2119015</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150324</t>
+          <t>2119015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54414</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>44566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72139</t>
+          <t>77965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>90900</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108119</t>
+          <t>109074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>133348</t>
+          <t>149675</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87957</t>
+          <t>127741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162801</t>
+          <t>177371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>650266</t>
+          <t>744298</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632541</t>
+          <t>725108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664053</t>
+          <t>758507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>854432</t>
+          <t>721359</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>825247</t>
+          <t>703185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>898845</t>
+          <t>735714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1504698</t>
+          <t>1465657</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1475245</t>
+          <t>1437961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1550089</t>
+          <t>1487591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37490</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>65091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>123713</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>113609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147566</t>
+          <t>151213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>172476</t>
+          <t>182692</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147385</t>
+          <t>161256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199820</t>
+          <t>205566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>876862</t>
+          <t>938704</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>862277</t>
+          <t>923769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888135</t>
+          <t>949810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>970659</t>
+          <t>985944</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946806</t>
+          <t>967267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995181</t>
+          <t>1004871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1847521</t>
+          <t>1924649</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820177</t>
+          <t>1901775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872612</t>
+          <t>1946085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925625</t>
+          <t>988860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094372</t>
+          <t>1118480</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094372</t>
+          <t>1118480</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094372</t>
+          <t>1118480</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019997</t>
+          <t>2107341</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019997</t>
+          <t>2107341</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019997</t>
+          <t>2107341</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144095</t>
+          <t>176467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218060</t>
+          <t>233558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293952</t>
+          <t>372575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409591</t>
+          <t>438334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>480796</t>
+          <t>560588</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614848</t>
+          <t>646768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3270777</t>
+          <t>3328588</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3240551</t>
+          <t>3298002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3314516</t>
+          <t>3355093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,34 +8089,34 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3330545</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3250736</t>
+          <t>3295014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3366375</t>
+          <t>3360773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>7912</t>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6565947</t>
+          <t>6659134</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6504090</t>
+          <t>6618141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6638142</t>
+          <t>6704321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
